--- a/artfynd/A 56870-2024 artfynd.xlsx
+++ b/artfynd/A 56870-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -798,6 +798,137 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>122001972</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56270</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Dokumentation efterfrågas</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>detektor med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Forsbacka-Väg 599, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>605276</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6721122</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Valbo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-06-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>01:20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Fladdermusinventering. Ekologigruppen AB</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Stina Hällholm</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Stina Hällholm, Lark Davis</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 56870-2024 artfynd.xlsx
+++ b/artfynd/A 56870-2024 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>122001972</v>
       </c>
       <c r="B3" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
